--- a/output/Complete_Coverage_Analysis_Results.xlsx
+++ b/output/Complete_Coverage_Analysis_Results.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://adminliveunc-my.sharepoint.com/personal/beibo_ad_unc_edu/Documents/CSCC/HCHS/V3_SIM/suddan/HCHS_simulation/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4" documentId="11_9E5A69C6DEAB4B252580C1EA27E95721F04F6915" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C4455239-9D4E-4C22-AC9E-E90A32A01FD1}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_2F013410A805BB5DE16B8BC222376979B92E257A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8E2D88ED-A752-44F5-BF54-620509DFF1C3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2401,8 +2401,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2781,16 +2784,16 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -2799,13 +2802,13 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -2864,7 +2867,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -2873,7 +2876,7 @@
         <v>4</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M3">
         <v>6</v>
@@ -2917,10 +2920,10 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -2932,7 +2935,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -3003,7 +3006,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -3012,7 +3015,7 @@
         <v>0</v>
       </c>
       <c r="M5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N5">
         <v>1</v>
@@ -3030,7 +3033,7 @@
         <v>2</v>
       </c>
       <c r="S5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T5">
         <v>0</v>
@@ -3050,22 +3053,22 @@
         <v>26</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>7</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -3074,10 +3077,10 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M6">
         <v>6</v>
@@ -3086,13 +3089,13 @@
         <v>6</v>
       </c>
       <c r="O6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="P6">
         <v>6</v>
       </c>
       <c r="Q6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="R6">
         <v>5</v>
@@ -3121,22 +3124,22 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -3151,10 +3154,10 @@
         <v>5</v>
       </c>
       <c r="N7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="O7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="P7">
         <v>3</v>
@@ -3166,7 +3169,7 @@
         <v>2</v>
       </c>
       <c r="S7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7">
         <v>0</v>
@@ -3703,7 +3706,7 @@
         <v>81</v>
       </c>
       <c r="O11" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -4032,7 +4035,7 @@
         <v>94</v>
       </c>
       <c r="O18" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
@@ -4361,7 +4364,7 @@
         <v>105</v>
       </c>
       <c r="O25" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
@@ -4690,7 +4693,7 @@
         <v>115</v>
       </c>
       <c r="O32" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -5677,7 +5680,7 @@
         <v>94</v>
       </c>
       <c r="O53" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
@@ -6006,7 +6009,7 @@
         <v>105</v>
       </c>
       <c r="O60" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -6335,7 +6338,7 @@
         <v>115</v>
       </c>
       <c r="O67" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
@@ -8790,7 +8793,7 @@
         <v>81</v>
       </c>
       <c r="O48" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -9448,7 +9451,7 @@
         <v>105</v>
       </c>
       <c r="O62" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
@@ -9777,7 +9780,7 @@
         <v>115</v>
       </c>
       <c r="O69" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
@@ -10493,7 +10496,7 @@
         <v>81</v>
       </c>
       <c r="O13" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
@@ -10540,7 +10543,7 @@
         <v>81</v>
       </c>
       <c r="O14" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -10587,7 +10590,7 @@
         <v>81</v>
       </c>
       <c r="O15" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
@@ -10822,7 +10825,7 @@
         <v>94</v>
       </c>
       <c r="O20" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
@@ -12138,7 +12141,7 @@
         <v>81</v>
       </c>
       <c r="O48" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
@@ -15627,7 +15630,7 @@
         <v>94</v>
       </c>
       <c r="O51" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
@@ -16860,7 +16863,7 @@
         <v>57</v>
       </c>
       <c r="O6" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -17095,7 +17098,7 @@
         <v>81</v>
       </c>
       <c r="O11" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
@@ -17894,7 +17897,7 @@
         <v>105</v>
       </c>
       <c r="O28" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
@@ -17988,7 +17991,7 @@
         <v>115</v>
       </c>
       <c r="O30" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
@@ -18082,7 +18085,7 @@
         <v>115</v>
       </c>
       <c r="O32" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
@@ -18411,7 +18414,7 @@
         <v>57</v>
       </c>
       <c r="O39" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
@@ -18505,7 +18508,7 @@
         <v>57</v>
       </c>
       <c r="O41" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
@@ -19398,7 +19401,7 @@
         <v>105</v>
       </c>
       <c r="O60" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
@@ -19727,7 +19730,7 @@
         <v>115</v>
       </c>
       <c r="O67" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
@@ -20396,7 +20399,7 @@
         <v>81</v>
       </c>
       <c r="O10" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
@@ -20490,7 +20493,7 @@
         <v>81</v>
       </c>
       <c r="O12" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
@@ -20678,7 +20681,7 @@
         <v>94</v>
       </c>
       <c r="O16" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -21148,7 +21151,7 @@
         <v>105</v>
       </c>
       <c r="O26" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
@@ -21477,7 +21480,7 @@
         <v>115</v>
       </c>
       <c r="O33" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
@@ -22041,7 +22044,7 @@
         <v>81</v>
       </c>
       <c r="O45" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
@@ -23379,7 +23382,7 @@
         <v>7</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3">
         <v>0.95</v>
@@ -23417,7 +23420,7 @@
         <v>7</v>
       </c>
       <c r="I4">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J4">
         <v>0.78885714285714303</v>
@@ -23455,7 +23458,7 @@
         <v>7</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0.95096652520000002</v>
@@ -23493,7 +23496,7 @@
         <v>7</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
         <v>0.94957142857142895</v>
@@ -23607,7 +23610,7 @@
         <v>7</v>
       </c>
       <c r="I9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="J9">
         <v>0.78271428571428603</v>
@@ -23645,7 +23648,7 @@
         <v>7</v>
       </c>
       <c r="I10">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J10">
         <v>0.95031055900000005</v>
@@ -23683,7 +23686,7 @@
         <v>7</v>
       </c>
       <c r="I11">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J11">
         <v>0.95014285714285696</v>
@@ -24329,7 +24332,7 @@
         <v>7</v>
       </c>
       <c r="I28">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J28">
         <v>0.878714285714286</v>
@@ -24443,7 +24446,7 @@
         <v>7</v>
       </c>
       <c r="I31">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J31">
         <v>0.878714285714286</v>
@@ -24899,7 +24902,7 @@
         <v>7</v>
       </c>
       <c r="I43">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J43">
         <v>0.92971428571428605</v>
@@ -24937,7 +24940,7 @@
         <v>7</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J44">
         <v>0.83385714285714296</v>
@@ -25089,7 +25092,7 @@
         <v>7</v>
       </c>
       <c r="I48">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J48">
         <v>0.92985714285714305</v>
@@ -25887,7 +25890,7 @@
         <v>7</v>
       </c>
       <c r="I69">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J69">
         <v>0.94328571428571395</v>
@@ -26001,7 +26004,7 @@
         <v>7</v>
       </c>
       <c r="I72">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J72">
         <v>0.92714285714285705</v>
@@ -26229,7 +26232,7 @@
         <v>7</v>
       </c>
       <c r="I78">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J78">
         <v>0.95528571428571396</v>
@@ -26381,7 +26384,7 @@
         <v>7</v>
       </c>
       <c r="I82">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J82">
         <v>0.91171428571428603</v>
@@ -26419,7 +26422,7 @@
         <v>7</v>
       </c>
       <c r="I83">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J83">
         <v>0.94371428571428595</v>
@@ -26495,7 +26498,7 @@
         <v>7</v>
       </c>
       <c r="I85">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J85">
         <v>0.94626623375714303</v>
@@ -26571,7 +26574,7 @@
         <v>7</v>
       </c>
       <c r="I87">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J87">
         <v>0.91242857142857103</v>
@@ -26685,7 +26688,7 @@
         <v>7</v>
       </c>
       <c r="I90">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J90">
         <v>0.94626623377142904</v>
@@ -26723,7 +26726,7 @@
         <v>7</v>
       </c>
       <c r="I91">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J91">
         <v>0.94614285714285695</v>
@@ -26837,7 +26840,7 @@
         <v>7</v>
       </c>
       <c r="I94">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J94">
         <v>0.63142857142857101</v>
@@ -26913,7 +26916,7 @@
         <v>7</v>
       </c>
       <c r="I96">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J96">
         <v>0.41485714285714298</v>
@@ -27179,7 +27182,7 @@
         <v>7</v>
       </c>
       <c r="I103">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J103">
         <v>0.93657142857142905</v>
@@ -27217,7 +27220,7 @@
         <v>7</v>
       </c>
       <c r="I104">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J104">
         <v>0.94057142857142895</v>
@@ -27255,7 +27258,7 @@
         <v>7</v>
       </c>
       <c r="I105">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J105">
         <v>0.93717532467142906</v>
@@ -27293,7 +27296,7 @@
         <v>7</v>
       </c>
       <c r="I106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J106">
         <v>0.93814285714285695</v>
@@ -27369,7 +27372,7 @@
         <v>7</v>
       </c>
       <c r="I108">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J108">
         <v>0.94128571428571395</v>
@@ -27559,7 +27562,7 @@
         <v>7</v>
       </c>
       <c r="I113">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="J113">
         <v>0.90185714285714302</v>
@@ -27597,7 +27600,7 @@
         <v>7</v>
       </c>
       <c r="I114">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J114">
         <v>0.91200000000000003</v>
@@ -27749,7 +27752,7 @@
         <v>7</v>
       </c>
       <c r="I118">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J118">
         <v>0.95685714285714296</v>
@@ -27885,45 +27888,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="2" max="2" width="39.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -28049,7 +28049,7 @@
         <v>25</v>
       </c>
       <c r="C5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D5">
         <v>1</v>
@@ -28067,7 +28067,7 @@
         <v>2</v>
       </c>
       <c r="I5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5">
         <v>0</v>
@@ -28093,13 +28093,13 @@
         <v>6</v>
       </c>
       <c r="E6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>6</v>
       </c>
       <c r="G6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H6">
         <v>5</v>
@@ -28128,10 +28128,10 @@
         <v>5</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
         <v>3</v>
@@ -28143,7 +28143,7 @@
         <v>2</v>
       </c>
       <c r="I7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -28165,45 +28165,42 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:L7"/>
   <sheetFormatPr defaultColWidth="11.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="3" max="12" width="20.7109375" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" ht="60" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>37</v>
       </c>
     </row>
@@ -28218,16 +28215,16 @@
         <v>3</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2">
         <v>4</v>
@@ -28236,13 +28233,13 @@
         <v>0</v>
       </c>
       <c r="J2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="K2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -28271,7 +28268,7 @@
         <v>4</v>
       </c>
       <c r="I3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J3">
         <v>4</v>
@@ -28280,7 +28277,7 @@
         <v>4</v>
       </c>
       <c r="L3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
@@ -28294,10 +28291,10 @@
         <v>6</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F4">
         <v>3</v>
@@ -28309,7 +28306,7 @@
         <v>6</v>
       </c>
       <c r="I4">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J4">
         <v>5</v>
@@ -28350,7 +28347,7 @@
         <v>0</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K5">
         <v>0</v>
@@ -28367,22 +28364,22 @@
         <v>26</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>7</v>
       </c>
       <c r="F6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G6">
         <v>2</v>
       </c>
       <c r="H6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I6">
         <v>1</v>
@@ -28391,10 +28388,10 @@
         <v>7</v>
       </c>
       <c r="K6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
@@ -28408,22 +28405,22 @@
         <v>2</v>
       </c>
       <c r="D7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7">
         <v>2</v>
       </c>
       <c r="I7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7">
         <v>0</v>
@@ -33154,7 +33151,7 @@
         <v>105</v>
       </c>
       <c r="O29" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
@@ -38816,7 +38813,7 @@
         <v>57</v>
       </c>
       <c r="O7" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
@@ -40790,7 +40787,7 @@
         <v>81</v>
       </c>
       <c r="O49" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
@@ -42587,7 +42584,7 @@
         <v>94</v>
       </c>
       <c r="O16" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
@@ -43527,7 +43524,7 @@
         <v>115</v>
       </c>
       <c r="O36" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
@@ -45841,7 +45838,7 @@
         <v>81</v>
       </c>
       <c r="O14" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
@@ -46217,7 +46214,7 @@
         <v>94</v>
       </c>
       <c r="O22" t="s">
-        <v>58</v>
+        <v>74</v>
       </c>
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
@@ -47486,7 +47483,7 @@
         <v>81</v>
       </c>
       <c r="O49" t="s">
-        <v>74</v>
+        <v>58</v>
       </c>
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
